--- a/tests/fixtures/extract_corpus_v2/dev/bundle_nasa_fea_011/extracted.xlsx
+++ b/tests/fixtures/extract_corpus_v2/dev/bundle_nasa_fea_011/extracted.xlsx
@@ -284,6 +284,11 @@
         <t>[Extract] | Confidence: 50%</t>
       </text>
     </comment>
+    <comment ref="K3" authorId="0" shapeId="0">
+      <text>
+        <t>[Extract] | Confidence: 50%</t>
+      </text>
+    </comment>
     <comment ref="L3" authorId="0" shapeId="0">
       <text>
         <t>[Extract] | Confidence: 50%</t>
@@ -359,21 +364,6 @@
         <t>[Extract] | Confidence: 50%</t>
       </text>
     </comment>
-    <comment ref="A7" authorId="0" shapeId="0">
-      <text>
-        <t>[Extract] | Confidence: 50%</t>
-      </text>
-    </comment>
-    <comment ref="B7" authorId="0" shapeId="0">
-      <text>
-        <t>[Extract] | Confidence: 50%</t>
-      </text>
-    </comment>
-    <comment ref="D7" authorId="0" shapeId="0">
-      <text>
-        <t>[Extract] | Confidence: 50%</t>
-      </text>
-    </comment>
   </commentList>
 </comments>
 </file>
@@ -525,11 +515,6 @@
       </text>
     </comment>
     <comment ref="F6" authorId="0" shapeId="0">
-      <text>
-        <t>[Extract] | Confidence: 50%</t>
-      </text>
-    </comment>
-    <comment ref="G6" authorId="0" shapeId="0">
       <text>
         <t>[Extract] | Confidence: 50%</t>
       </text>
@@ -1331,12 +1316,12 @@
       </c>
       <c r="B3" s="12" t="inlineStr">
         <is>
-          <t>FEA of Ti-6Al-4V reaction wheel bracket for quasi-static launch load margin and local mode frequency assessment</t>
+          <t>FEA of Ti-6Al-4V reaction wheel bracket for quasi-static launch load strength margins and local modal frequency for 12U SmallSat flight clearance</t>
         </is>
       </c>
       <c r="C3" s="12" t="inlineStr">
         <is>
-          <t>Finite element model (Abaqus/Standard 2023 HF4) of the RWA-3 bracket on a 12U SmallSat avionics deck. Used to demonstrate positive yield margin under 10g axial / 8g lateral / 6g transverse quasi-static launch loads per LV-STD-129, verify first local mode above 500 Hz, and compare stress/strain predictions against bench-test measurements for flight clearance of bracket lot S/Ns RWB-052 through -058.</t>
+          <t>Finite element model (Abaqus/Standard 2023 HF4) of the RWA-3 bracket (P/N RWB-402123 Rev B) is used to demonstrate positive yield margin under 10g/8g/6g quasi-static launch loads per LV-STD-129 and to verify the first local bracket mode exceeds 500 Hz. Predictions are anchored to bench strain-gage and tap-test data. Results support flight clearance for bracket serial numbers RWB-052 through -058. Fatigue and pyroshock are explicitly out of scope.</t>
         </is>
       </c>
       <c r="D3" s="12" t="inlineStr">
@@ -1351,12 +1336,12 @@
       </c>
       <c r="F3" s="12" t="inlineStr">
         <is>
-          <t>MRL 4</t>
+          <t>MRL 3</t>
         </is>
       </c>
       <c r="G3" s="12" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="H3" s="12" t="inlineStr">
@@ -1374,9 +1359,9 @@
           <t>Date of this assessment (YYYY-MM-DD)</t>
         </is>
       </c>
-      <c r="K3" s="3" t="inlineStr">
-        <is>
-          <t>DOI, report number, or URI</t>
+      <c r="K3" s="12" t="inlineStr">
+        <is>
+          <t>report.md — Credibility Assessment Report, FEA of Reaction Wheel Bracket for 12U SmallSat, Model ID FE-RWA3-BRK-021 Rev C, dated 2026-07-31</t>
         </is>
       </c>
       <c r="L3" s="12" t="inlineStr">
@@ -1437,7 +1422,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:F6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1495,7 +1480,7 @@
       </c>
       <c r="B3" s="12" t="inlineStr">
         <is>
-          <t>LV-STD-129 / NASA-STD-5011 Strength and Stiffness Requirements</t>
+          <t>Structural performance requirements for RWA-3 bracket flight clearance</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
@@ -1505,7 +1490,7 @@
       </c>
       <c r="D3" s="12" t="inlineStr">
         <is>
-          <t>Bracket must show positive yield margin under 1.4x quasi-static launch loads (10g axial, 8g lateral, 6g transverse) and first local mode must exceed 500 Hz to avoid coupling with bus modes.</t>
+          <t>Bracket must show positive yield margin (≥0) at 1.4x limit quasi-static loads (10g axial, 8g lateral, 6g transverse) and first local bracket mode must exceed 500 Hz; model strain predictions must agree with bench test within 10% and mode frequency within 5%; mesh GCI must be &lt;10% at hotspot.</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
@@ -1532,7 +1517,7 @@
       </c>
       <c r="D4" s="13" t="inlineStr">
         <is>
-          <t>Abaqus/Standard 2023 HF4 FEA model of the Ti-6Al-4V RWA-3 bracket with C3D10 elements, S8R shell equivalent deck, beam connector fasteners, and frictional contact interface.</t>
+          <t>Abaqus/Standard 2023 HF4 finite element model of Ti-6Al-4V reaction wheel bracket with beam-connector fasteners, frictional contact, and orthotropic equivalent deck plate; used for static stress and normal-mode analysis.</t>
         </is>
       </c>
     </row>
@@ -1544,12 +1529,12 @@
       </c>
       <c r="B5" s="13" t="inlineStr">
         <is>
-          <t>INP-RWA3-015 Input Ledger</t>
+          <t>INP-RWA3-015 input ledger and bench test data (LIB-STR-2026)</t>
         </is>
       </c>
       <c r="D5" s="13" t="inlineStr">
         <is>
-          <t>Catalogued input parameters including MMPDS-17 Ti-6Al-4V material properties, bolt preload torque-tension data, friction coefficients from ECSS-Q-70-71A coupon tests, load factors, and geometry from P/N RWB-402123 Rev B.</t>
+          <t>Catalogued material properties (MMPDS-17), bolt preload torque-to-tension measurements, interface friction coupon data, mass simulator inertia verification, raw strain rosette time series, FFT modal data, and calibration certificates for all test instrumentation.</t>
         </is>
       </c>
     </row>
@@ -1561,29 +1546,12 @@
       </c>
       <c r="B6" s="13" t="inlineStr">
         <is>
-          <t>RWA3 Bracket Bench Test Data</t>
+          <t>NAFEMS benchmarks and internal verification records</t>
         </is>
       </c>
       <c r="D6" s="13" t="inlineStr">
         <is>
-          <t>Static pull test and modal tap test results for production bracket S/N RWB-053, including strain rosette readings at G1 and G2, triaxial accelerometer modal data, and ultrasonic bolt elongation measurements.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="13" t="inlineStr">
-        <is>
-          <t>Dataset</t>
-        </is>
-      </c>
-      <c r="B7" s="13" t="inlineStr">
-        <is>
-          <t>VVP-PL-021 NAFEMS Benchmark Records</t>
-        </is>
-      </c>
-      <c r="D7" s="13" t="inlineStr">
-        <is>
-          <t>Benchmark verification results for Abaqus features used (NAFEMS-R0040, NAFEMS-R0051, internal bolted-joint BJ-VAL-07), rerun in 2025 with hash records confirming solver build consistency.</t>
+          <t>Benchmark problems (cantilever, plate-with-hole, bolted-joint pull test) rerun against Abaqus 2023 HF4; results and checksums archived in VVP-PL-021 Appendix B; maximum deviations 3.4% frequency, 5.8% stress.</t>
         </is>
       </c>
     </row>
@@ -2020,7 +1988,7 @@
     <row r="3">
       <c r="A3" s="12" t="inlineStr">
         <is>
-          <t>Static Strain Gage Comparison</t>
+          <t>Static strain gage comparison — bench test vs FEA</t>
         </is>
       </c>
       <c r="B3" s="12" t="inlineStr">
@@ -2035,7 +2003,7 @@
       </c>
       <c r="D3" s="12" t="inlineStr">
         <is>
-          <t>Production bracket (S/N RWB-053) subjected to 210 N vertical load simulating ~10g. Principal strains at rosette G1 (inner fillet near Bolt B3) and G2 (outer web) measured and compared to M3 model predictions with test-matched preload settings.</t>
+          <t>Production bracket S/N RWB-053 subjected to 210 N vertical load (approx. 10g) on a fixture replicating deck boundary. Two 3-element strain rosettes measured principal strains at the critical inner fillet (G1) and outer web (G2). FEA predictions on M3 mesh with test-matched preload settings were compared to measured values.</t>
         </is>
       </c>
       <c r="E3" s="12" t="inlineStr">
@@ -2050,12 +2018,12 @@
       </c>
       <c r="G3" s="12" t="inlineStr">
         <is>
-          <t>Load cell uncertainty ±1%; strain gage uncertainty 2%; input variability from 200-sample LHS propagation</t>
+          <t>Measurement uncertainty (2% gage) and Latin hypercube sensitivity (200 realizations on M2) combined with mesh GCI (5.6%) in quadrature; combined CV ~7.0% for peak stress</t>
         </is>
       </c>
       <c r="H3" s="12" t="inlineStr">
         <is>
-          <t>G1 model bias −4.3% (1755 με predicted vs 1820 με measured); G2 model +3.4% (703 με predicted vs 680 με measured); both within modeling plan acceptance criterion of ±10%</t>
+          <t>G1 error −4.3% (model 1755 με vs test 1820 με); G2 error +3.4% (model 703 με vs test 680 με); both within 10% acceptance criterion</t>
         </is>
       </c>
       <c r="I3" s="12" t="inlineStr">
@@ -2067,7 +2035,7 @@
     <row r="4">
       <c r="A4" s="13" t="inlineStr">
         <is>
-          <t>Modal Tap Test Comparison</t>
+          <t>Modal tap test — first local mode frequency comparison</t>
         </is>
       </c>
       <c r="B4" s="13" t="inlineStr">
@@ -2077,7 +2045,7 @@
       </c>
       <c r="D4" s="13" t="inlineStr">
         <is>
-          <t>First local mode frequency of the bracket-RWA subassembly extracted via impact hammer / triaxial accelerometer tap test on the same production test article and compared to Lanczos eigenanalysis on M3.</t>
+          <t>Impact hammer modal test on the same instrumented bracket fixture; triax accelerometer measured first local out-of-plane mode. FEA normal-modes result (Lanczos, M3 mesh, production preload, μ = 0.18) compared to measured frequency.</t>
         </is>
       </c>
       <c r="E4" s="13" t="inlineStr">
@@ -2092,12 +2060,12 @@
       </c>
       <c r="G4" s="13" t="inlineStr">
         <is>
-          <t>LHS sensitivity study showing frequency 5th percentile &gt; 590 Hz across input variability; preload dominant contributor (61%)</t>
+          <t>Latin hypercube propagation (200 samples); 5th percentile of predicted frequency distribution across input variability</t>
         </is>
       </c>
       <c r="H4" s="13" t="inlineStr">
         <is>
-          <t>Model predicted 603 Hz vs measured 620 Hz (−2.7%); within modeling plan criterion of ±5%</t>
+          <t>Model 603 Hz vs test 620 Hz; error −2.7%; 5th percentile of LHS distribution &gt;590 Hz; all samples exceed 500 Hz requirement</t>
         </is>
       </c>
       <c r="I4" s="13" t="inlineStr">
@@ -2109,7 +2077,7 @@
     <row r="5">
       <c r="A5" s="13" t="inlineStr">
         <is>
-          <t>Mesh Convergence Study (GCI)</t>
+          <t>Mesh convergence study and GCI estimation</t>
         </is>
       </c>
       <c r="B5" s="13" t="inlineStr">
@@ -2119,12 +2087,12 @@
       </c>
       <c r="D5" s="13" t="inlineStr">
         <is>
-          <t>Three systematically refined meshes (M1: 118k, M2: 462k, M3: 1.78M elements) generated with curvature-based sizing. Richardson extrapolation applied to peak von Mises stress at the G1 fillet hotspot under 10g axial case to quantify discretization error.</t>
+          <t>Three systematically refined meshes (M1: 118k, M2: 462k, M3: 1.78M elements) generated with curvature-based sizing. Peak von Mises stress at the G1 hotspot and first local mode frequency tracked across meshes. Richardson extrapolation performed to quantify discretization error.</t>
         </is>
       </c>
       <c r="E5" s="13" t="inlineStr">
         <is>
-          <t>Richardson extrapolated (theoretical exact) solution; observed convergence order p = 1.83</t>
+          <t>Richardson extrapolation extrapolated value; global strain energy convergence</t>
         </is>
       </c>
       <c r="F5" s="13" t="inlineStr">
@@ -2134,12 +2102,12 @@
       </c>
       <c r="G5" s="13" t="inlineStr">
         <is>
-          <t>Grid Convergence Index (GCI) with Richardson extrapolation at 95% CI</t>
+          <t>Grid Convergence Index (GCI) with Richardson extrapolation, observed convergence order p = 1.83</t>
         </is>
       </c>
       <c r="H5" s="13" t="inlineStr">
         <is>
-          <t>GCI = 5.6% at hotspot on M3; global strain energy variation &lt; 0.9% between M2 and M3; first local mode frequency shift +1.1% M2 to M3</t>
+          <t>GCI (95% CI) = 5.6% at hotspot on M3; global strain energy change M2→M3 &lt;0.9%; mode frequency shift M2→M3 = +1.1%</t>
         </is>
       </c>
       <c r="I5" s="13" t="inlineStr">
@@ -2151,7 +2119,7 @@
     <row r="6">
       <c r="A6" s="13" t="inlineStr">
         <is>
-          <t>Uncertainty Quantification — Latin Hypercube Sensitivity Study</t>
+          <t>Independent reviewer parallel model check</t>
         </is>
       </c>
       <c r="B6" s="13" t="inlineStr">
@@ -2161,27 +2129,22 @@
       </c>
       <c r="D6" s="13" t="inlineStr">
         <is>
-          <t>200-realization Latin hypercube sample on M2 spanning bolt preload, friction coefficient, fillet radius, elastic modulus, and load magnitude. Outputs tracked: peak von Mises stress, principal strains at gage locations, first local mode frequency.</t>
+          <t>Independent reviewer (J. Carver, not on design team) performed a cold read and model recreation using M2 mesh with node-to-surface contact discretization (vs. surface-to-surface in baseline). Hotspot location and stress magnitude compared to reported values.</t>
         </is>
       </c>
       <c r="E6" s="13" t="inlineStr">
         <is>
-          <t>Modeling plan acceptance criteria and flight requirement margins</t>
+          <t>Baseline FEA results from FE-RWA3-BRK-021 Rev C</t>
         </is>
       </c>
       <c r="F6" s="13" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G6" s="13" t="inlineStr">
-        <is>
-          <t>Latin hypercube sampling (LHS), standardized regression coefficients for sensitivity ranking, quadrature combination of mesh GCI and input variability</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H6" s="13" t="inlineStr">
         <is>
-          <t>Peak stress mean 260 MPa, σ = 18 MPa, 95th percentile 289 MPa (404 MPa at 1.4x load factor); combined CV ~7.0%; mode 5th percentile &gt; 590 Hz; strength margin at 95th percentile +1.05</t>
+          <t>Hotspot stress within 6% of reported value; hotspot location identical; review comments and closures in CR-REV-441</t>
         </is>
       </c>
       <c r="I6" s="13" t="inlineStr">
@@ -2193,7 +2156,7 @@
     <row r="7">
       <c r="A7" s="13" t="inlineStr">
         <is>
-          <t>Independent Reviewer Model Recreation</t>
+          <t>NAFEMS and internal benchmark verification</t>
         </is>
       </c>
       <c r="B7" s="13" t="inlineStr">
@@ -2203,12 +2166,12 @@
       </c>
       <c r="D7" s="13" t="inlineStr">
         <is>
-          <t>Independent reviewer J. Carver (not on design team) performed cold read and parallel model recreation using M2 mesh with different contact discretization (node-to-surface) to verify hotspot location and peak stress magnitude.</t>
+          <t>Abaqus 2023 HF4 features used in the model (C3D10, contact, beam connectors, normal modes) assessed against NAFEMS-R0040, NAFEMS-R0051, and internal bolted-joint pull test BJ-VAL-07. Patch test on custom bracket slice geometry also performed. Benchmarks rerun in 2025 with checksums recorded.</t>
         </is>
       </c>
       <c r="E7" s="13" t="inlineStr">
         <is>
-          <t>Primary analyst results from FE-RWA3-BRK-021 Rev C</t>
+          <t>NAFEMS benchmark reference solutions; analytical patch test (uniform strain)</t>
         </is>
       </c>
       <c r="F7" s="13" t="inlineStr">
@@ -2218,7 +2181,7 @@
       </c>
       <c r="H7" s="13" t="inlineStr">
         <is>
-          <t>Hotspot location and peak stress magnitude within 6% of reported values; review comments and closures in CR-REV-441</t>
+          <t>Max deviation 3.4% in mode frequency; 5.8% in stress concentration for coarse tetrahedral meshes; patch test within machine precision</t>
         </is>
       </c>
       <c r="I7" s="13" t="inlineStr">
@@ -2365,19 +2328,19 @@
         </is>
       </c>
       <c r="C5" s="14" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D5" s="14" t="n">
         <v>4</v>
       </c>
       <c r="E5" s="14" t="inlineStr">
         <is>
-          <t>Commercial solver with documented quality processes, verified features, no open defects affecting model elements used</t>
+          <t>Commercial solver used with documented quality records; no open defects affecting elements in use; version control for scripts</t>
         </is>
       </c>
       <c r="F5" s="14" t="inlineStr">
         <is>
-          <t>Abaqus/Standard 2023 HF4 used under documented license (SW-QA-102). No open SPRs affecting C3D10 or connector behavior per Dassault KB review as of 2026-06-15. Pre/post Python scripts versioned in GitLab (tag v2.3.1). NAFEMS benchmarks (NAFEMS-R0040, R0051, BJ-VAL-07) run in CI pipelines with zero regressions over 24 months; failures block tags. Execution environment documented; result reproducibility confirmed across two machines to 8 significant digits.</t>
+          <t>Abaqus/Standard 2023 HF4 is a widely certified commercial solver. License and feature codes documented in SW-QA-102. Dassault KB review confirmed no open SPRs affecting C3D10 or connector elements as of 2026-06-15. Pre/post Python scripts versioned in GitLab (tag v2.3.1). NAFEMS and internal benchmark problems run in CI pipeline on every commit; zero regressions over last 24 months on element types used. Reproducibility verified across two machines (ODB result checksums match to 8 significant digits). Execution environment documented (OS, hardware).</t>
         </is>
       </c>
       <c r="G5" s="14" t="inlineStr">
@@ -2399,19 +2362,19 @@
         </is>
       </c>
       <c r="C6" s="14" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D6" s="14" t="n">
         <v>4</v>
       </c>
       <c r="E6" s="14" t="inlineStr">
         <is>
-          <t>Benchmark comparisons to analytical or NAFEMS reference solutions within acceptable tolerances for element types and features used</t>
+          <t>Code verified against standard benchmark problems for element types and features used; deviations documented</t>
         </is>
       </c>
       <c r="F6" s="14" t="inlineStr">
         <is>
-          <t>NAFEMS-R0040 (cantilever beam) and NAFEMS-R0051 (plate with hole) benchmarks executed with same Abaqus build; maximum deviation 3.4% in mode frequency and 5.8% in stress concentration for coarse tetrahedral meshes. Internal bolted-joint benchmark BJ-VAL-07 also passed. Uniform strain patch test on a custom bracket slice geometry passed to machine precision. Benchmark hashes recorded in VVP-PL-021 Appendix B, rerun in 2025.</t>
+          <t>NAFEMS-R0040 (cantilever beam, displacement and stress), NAFEMS-R0051 (plate with hole), and internal bolted-joint pull test BJ-VAL-07 all completed against Abaqus 2023 HF4. Maximum deviations: 3.4% mode frequency, 5.8% stress (coarse tetrahedral). A uniform-strain patch test on a custom bracket slice geometry passed within machine precision. Results and file hashes archived in VVP-PL-021 Appendix B. Benchmarks rerun in 2025 with same build.</t>
         </is>
       </c>
       <c r="G6" s="14" t="inlineStr">
@@ -2433,19 +2396,19 @@
         </is>
       </c>
       <c r="C7" s="14" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D7" s="14" t="n">
         <v>4</v>
       </c>
       <c r="E7" s="14" t="inlineStr">
         <is>
-          <t>Mesh GCI &lt; 10% at critical hotspot; global strain energy variation &lt; 2% between finest meshes; modeling plan criterion met</t>
+          <t>GCI &lt; 10% at critical hotspot; global energy change &lt; 2% between finest meshes</t>
         </is>
       </c>
       <c r="F7" s="14" t="inlineStr">
         <is>
-          <t>Three systematically refined meshes (118k, 462k, 1.78M elements) with curvature-based sizing. Richardson extrapolation (observed order p = 1.83) yields GCI = 5.6% (95% CI) at the critical fillet on M3, within the modeling plan criterion of &lt; 10%. Global strain energy varied &lt; 0.9% between M2 and M3. First local mode frequency stabilized at M2; M3 shifted +1.1%. Mesh quality metrics (Jacobian &gt; 0.5, min corner angle &gt; 27°) documented.</t>
+          <t>Three systematically refined meshes (M1 118k, M2 462k, M3 1.78M elements) with curvature-based sizing at fillets and hole edges. Peak von Mises at G1 hotspot converged monotonically M1→M3. Richardson extrapolation (observed order p = 1.83) gives GCI (95% CI) = 5.6% on M3 — within the 10% acceptance criterion. Global strain energy change M2→M3 &lt;0.9%. First local mode frequency shift M2→M3 = +1.1%. Mesh quality metrics documented (min corner angle &gt;27°, Jacobian &gt;0.5). Reaction force balance error &lt;0.2% across all meshes.</t>
         </is>
       </c>
       <c r="G7" s="14" t="inlineStr">
@@ -2474,12 +2437,12 @@
       </c>
       <c r="E8" s="14" t="inlineStr">
         <is>
-          <t>Convergence achieved without cutbacks; residual tolerances documented; reaction force balance within acceptable error</t>
+          <t>Convergence achieved without cutbacks; residual force within tolerance; reaction force balance error &lt; 1%</t>
         </is>
       </c>
       <c r="F8" s="14" t="inlineStr">
         <is>
-          <t>Static general step converged in ≤ 6 nonlinear iterations per load case without cutbacks. Default 0.5% residual force tolerance applied. Reaction force balance error &lt; 0.2% across all meshes and cases. No contact chattering detected at nominal and μ ≥ 0.14; no negative eigenvalues in preloaded stiffness matrix. Kinetic energy fraction &lt; 0.3% of strain energy confirming quasi-static assumption. Lanczos extraction of 12 eigenpairs documented.</t>
+          <t>Static general step with automatic stabilization off; nonlinear iterations ≤6 per load case with no cutbacks on final mesh. Nonlinear tolerances at Abaqus default (0.5% residual force). Reaction force balance error &lt;0.2% in all runs. No negative eigenvalues in linear stiffness matrix for preloaded state. Kinetic energy fraction &lt;0.3% of strain energy confirming quasi-static behavior. No contact chattering at nominal preload. Low-friction extreme case (μ = 0.10) produced localized micro-slip but stress change &lt;2%. Lanczos eigensolver extracted 12 eigenpairs to 2000 Hz.</t>
         </is>
       </c>
       <c r="G8" s="14" t="inlineStr">
@@ -2501,19 +2464,19 @@
         </is>
       </c>
       <c r="C9" s="14" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D9" s="14" t="n">
         <v>4</v>
       </c>
       <c r="E9" s="14" t="inlineStr">
         <is>
-          <t>Independent model recreation confirms hotspot location and magnitude; boundary conditions and loads verified; modeling plan defines and closes all acceptance criteria</t>
+          <t>Independent review of model setup; boundary conditions and loads verified; mesh quality checked; post-processing reviewed</t>
         </is>
       </c>
       <c r="F9" s="14" t="inlineStr">
         <is>
-          <t>Independent reviewer (J. Carver, not on design team) performed cold read and parallel recreation on M2 with alternative contact discretization; hotspot location and magnitude within 6%. Review comments and closures in CR-REV-441. Modeling plan MVP-PL-342 Rev A defined acceptance criteria (strain ±10%, mode ±5%, GCI &lt; 10%); all criteria met. Inputs captured in versioned params.yml with hash; reproducible Python driver (run_case.py). Boundary conditions consistent with system ICD-AV-113 and test fixture definition.</t>
+          <t>Independent reviewer J. Carver (PhD, 18 years dynamics, not on design team) performed cold read and parallel model recreation on M2 with different contact discretization (node-to-surface); hotspot location and magnitude within 6%. Review comments and closure responses recorded in CR-REV-441. Modeling plan MVP-PL-342 Rev A defined acceptance criteria; all met. Boundary conditions consistent with ICD-AV-113 and test fixture interface definition. All inputs in parameter file (params.yml) with hash; solver launched via reproducible Python driver. Force balance error &lt;0.2% verifies load application. Configuration: analyst has NAFEMS Level 2 credential and documented advanced Abaqus training.</t>
         </is>
       </c>
       <c r="G9" s="14" t="inlineStr">
@@ -2535,19 +2498,19 @@
         </is>
       </c>
       <c r="C10" s="14" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D10" s="14" t="n">
         <v>3</v>
       </c>
       <c r="E10" s="14" t="inlineStr">
         <is>
-          <t>Governing equations and modeling choices justified; known limitations documented; applicability to COU confirmed</t>
+          <t>Governing physics and modeling approach justified; known limitations documented with impact assessed</t>
         </is>
       </c>
       <c r="F10" s="14" t="inlineStr">
         <is>
-          <t>Linear elasticity with geometric linearity justified for yield-margin assessment (stresses well below yield in nominal case). C3D10 quadratic tetrahedral elements, S8R shells for equivalent deck, and beam connectors for bolts are documented and benchmarked. Known omissions explicitly stated: threads and hole bearing not resolved (acceptable for bracket-level margins; fatigue out of scope), damping excluded (frequencies only used), temperature dependence limited to single E perturbation (justified by &lt; 15 C variation, THM-TR-115). Historical precedent from Aurora-4 CubeSat bracket supports this modeling approach. Does not achieve level 5 because thread/bearing effects are acknowledged approximations without formal bounding analysis of their effect on stress distribution.</t>
+          <t>Linear elasticity with geometric nonlinearity off is justified given small deformation regime at launch loads. C3D10 quadratic tetrahedral elements used for bracket (appropriate for stress concentration resolution); S8R shell for equivalent deck plate; beam connectors for bolts with calibrated stiffness. Frictional contact with Coulomb model is standard for preloaded bolted joints. Known omissions explicitly documented: no thread bending or hole bearing (compensated by A-basis allowables and test comparison), no damping in modes (only frequencies used), single E perturbation for temperature. Bus flexibility excluded from local modes with rationale (handled in system IFEM). Physical load path narrative provided and confirmed by test data. Method has prior flight heritage (Aurora-4 CubeSat bracket, 2019, 5 flight units, no anomalies).</t>
         </is>
       </c>
       <c r="G10" s="14" t="inlineStr">
@@ -2569,19 +2532,19 @@
         </is>
       </c>
       <c r="C11" s="14" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D11" s="14" t="n">
         <v>4</v>
       </c>
       <c r="E11" s="14" t="inlineStr">
         <is>
-          <t>All key inputs traceable to aerospace-standard sources or measured data; uncertainty characterized for dominant contributors</t>
+          <t>Material properties from authoritative source; fastener preload from measurement; input uncertainties characterized</t>
         </is>
       </c>
       <c r="F11" s="14" t="inlineStr">
         <is>
-          <t>Ti-6Al-4V material from MMPDS-17 (A-basis, Table 2.3.1.0(b)); elastic modulus mean 114 GPa, CV 3%. Bolt preload from torque-tension correlation measured on five samples with ultrasonic elongation (k = 0.20 ± 0.03, resulting 4.5 kN ± 0.45 kN). Friction coefficient from ECSS-Q-70-71A with in-house coupon measurements (μ range 0.14–0.22). Mass inertia verified by torsional pendulum test. Load factors per LV-STD-129 and ICD-AV-113. Fillet radius uncertainty from machining tolerance stack (1.50 mm ± 0.15 mm). All inputs catalogued in INP-RWA3-015 with citations and file paths.</t>
+          <t>Ti-6Al-4V E and density from MMPDS-17 (A-basis allowables); Poisson's ratio 0.34 documented. Bolt preload (4.5 kN mean, 1σ = 0.45 kN) from torque-to-tension measurement on five samples using ultrasonic elongation monitoring; k-factor 0.20 ± 0.03. Interface friction μ = 0.18 from ECSS-Q-70-71A with in-house coupon testing (0.14–0.22 range). Mass simulator 2.10 kg ± 0.02 kg verified by torsional pendulum test. Load factors from LV-STD-129 with 1.4x limit loads per NASA-STD-5011. All values catalogued in input ledger INP-RWA3-015 with citations and file paths. Conservative (A-basis or tail) selections made where ambiguity exists.</t>
         </is>
       </c>
       <c r="G11" s="14" t="inlineStr">
@@ -2610,12 +2573,12 @@
       </c>
       <c r="E12" s="14" t="inlineStr">
         <is>
-          <t>Test article is production-representative with documented configuration; surface finish and fastener class match flight configuration</t>
+          <t>Test article is production-representative; surface finish and fastener class match flight configuration</t>
         </is>
       </c>
       <c r="F12" s="14" t="inlineStr">
         <is>
-          <t>Single production bracket (S/N RWB-053) from the flight lot used as test article, with production fasteners (M5 × 0.8 class 12.9) and Alodine surface finish. Bolt preload confirmed by ultrasonic elongation monitoring during test. Mass simulator matched to RWA inertia spec (RWA-DWG-812). Configuration is production-representative. Only one specimen tested, limiting statistical characterization of unit-to-unit variability; this is partially compensated by LHS uncertainty propagation over bolt preload and fillet radius distributions. Historical Aurora-4 data provides additional precedent.</t>
+          <t>Test article is a production bracket (S/N RWB-053) from the same manufacturing lot as flight units (RWB-052 through -058), with production fasteners (M5 × 0.8 class 12.9) and Alodine surface finish. One bracket was tested (n = 1); no explicit statistical characterization of sample-to-sample variability in the bracket itself, though manufacturing tolerance variability (fillet radius, hole position) is captured in the LHS uncertainty propagation. Ultrasonic bolt elongation monitoring confirmed preload on test article. Test article is within the scope of flight lot.</t>
         </is>
       </c>
       <c r="G12" s="14" t="inlineStr">
@@ -2644,12 +2607,12 @@
       </c>
       <c r="E13" s="14" t="inlineStr">
         <is>
-          <t>Instrumentation calibrated; load application and boundary conditions controlled and documented; measurement uncertainties quantified</t>
+          <t>Calibrated instrumentation; controlled load application; measurement uncertainties reported; test protocol documented</t>
         </is>
       </c>
       <c r="F13" s="14" t="inlineStr">
         <is>
-          <t>Dedicated fixture replicating deck boundary condition. Load cell accuracy ±1%; strain rosette uncertainty 2% (2σ = ±36 με at G1, ±14 με at G2). Impact hammer with force transducer for modal test; first local mode frequency uncertainty ±6 Hz. Ultrasonic bolt elongation monitoring for preload verification. No slip or seating shifts after two load-unload cycles (residual &lt; 10 με). Calibration certificates stored in SharePoint LIB-STR-2026 with data lineage map. Test conditions controlled but limited to a single static load direction and single modal extraction; full three-axis quasi-static loading not physically tested.</t>
+          <t>Static test used a dedicated fixture replicating deck boundary. Load cell accuracy ±1%. Two 3-element strain rosettes (G1, G2) with measurement uncertainty ±2% (±36 με at G1, ±14 με at G2). Triax accelerometer and calibrated impact hammer with force transducer for modal test. Modal frequency measured at 620 Hz ± 6 Hz with clear single-DOF peak. No visible slip or seating after two load-unload cycles; residual strain &lt;10 με. Raw strain time series and FFTs stored in SharePoint LIB-STR-2026 with calibration certificates. Test conducted per the boundary conditions defined in ICD-AV-113. Formal test standard (ASTM/ISO) not explicitly cited, but instrumentation and protocol are documented.</t>
         </is>
       </c>
       <c r="G13" s="14" t="inlineStr">
@@ -2671,19 +2634,19 @@
         </is>
       </c>
       <c r="C14" s="14" t="n">
+        <v>3</v>
+      </c>
+      <c r="D14" s="14" t="n">
         <v>4</v>
       </c>
-      <c r="D14" s="14" t="n">
-        <v>3</v>
-      </c>
       <c r="E14" s="14" t="inlineStr">
         <is>
-          <t>Model inputs for validation runs set to match measured test conditions; discrepancies identified and propagated into uncertainty budget</t>
+          <t>Model boundary conditions match test fixture; model inputs set to test-measured values for comparison runs</t>
         </is>
       </c>
       <c r="F14" s="14" t="inlineStr">
         <is>
-          <t>Model run with test-preload settings (4.3 kN per KB review of ultrasonic data) matching measured bolt preload for the static comparison. Deck boundary condition replicated per fixture definition. Load magnitude (210 N) matched to load cell reading. Mass proxy inertia matched to RWA spec. Observed strain bias at G1 (−4.3%) not bias-corrected in the model but carried as an identified discrepancy into the total uncertainty budget. Input parameter comparison documented in report Sections 5–6. Does not reach level 4 because full three-axis test conditions were not matched (only vertical load tested), and friction coefficient was not independently measured during the test run.</t>
+          <t>Deck boundary in FEA fixed at mounting hole rings consistent with test fixture interface definition. Comparison runs used test-measured preload settings (4.3 kN, confirmed by ultrasonic monitoring). Mass proxy inertia matched to RWA spec and verified. Load magnitude 210 N (10g equivalent) applied through RWA CG consistent with test load applicator geometry. Friction coefficient set to nominal 0.18 matching Alodine-treated Ti-Ti surface condition of test article. Input ledger INP-RWA3-015 explicitly documents the mapping between test conditions and model parameters. Measurement uncertainties (preload, load, gage) are propagated and reported.</t>
         </is>
       </c>
       <c r="G14" s="14" t="inlineStr">
@@ -2705,19 +2668,19 @@
         </is>
       </c>
       <c r="C15" s="14" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D15" s="14" t="n">
         <v>4</v>
       </c>
       <c r="E15" s="14" t="inlineStr">
         <is>
-          <t>Quantitative comparison at multiple locations; errors within modeling plan criterion of ±10% for strain and ±5% for mode frequency; uncertainty bands reported</t>
+          <t>Strain predictions within 10% of test; mode frequency within 5%; quantitative metrics reported with uncertainty</t>
         </is>
       </c>
       <c r="F15" s="14" t="inlineStr">
         <is>
-          <t>Strain comparison at two rosette locations: G1 bias −4.3% (within ±10% criterion), G2 bias +3.4% (within ±10% criterion). Modal frequency bias −2.7% (within ±5% criterion). Measurement uncertainties quantified (2% strain, ±6 Hz modal). Model bias and gage uncertainty combined in total uncertainty budget. LHS study provides full output distribution (mean, σ, 95th percentile) for peak stress and mode frequency. Combined CV ~7.0% for peak stress after quadrature combination of mesh GCI and input variability. Strength margin +1.05 at 95th percentile with A-basis allowables. All acceptance criteria from MVP-PL-342 met.</t>
+          <t>G1 fillet principal strain: model 1755 με vs test 1820 με, error −4.3% (within 10% criterion). G2 web principal strain: model 703 με vs test 680 με, error +3.4% (within 10% criterion). First local mode: model 603 Hz vs test 620 Hz, error −2.7% (within 5% criterion). All modeling plan acceptance criteria met. Combined uncertainty budget (mesh GCI 5.6% + input variability CV ~7%) reported for peak stress. Measurement uncertainties quantified at each comparison point. Small conservative bias at G1 (model under-predicts by 4.3%) documented and carried into uncertainty budget rather than bias-corrected. Independent reviewer confirmed hotspot location and stress level independently.</t>
         </is>
       </c>
       <c r="G15" s="14" t="inlineStr">
@@ -2739,19 +2702,19 @@
         </is>
       </c>
       <c r="C16" s="14" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D16" s="14" t="n">
         <v>4</v>
       </c>
       <c r="E16" s="14" t="inlineStr">
         <is>
-          <t>QoIs directly measure the safety and performance concerns (yield margin and mode frequency); computable from model and measurable in test</t>
+          <t>QoIs directly map to the safety and performance requirements (yield margin, modal frequency); measurable both computationally and experimentally</t>
         </is>
       </c>
       <c r="F16" s="14" t="inlineStr">
         <is>
-          <t>QoIs are peak von Mises stress at the critical fillet (mapped to yield margin via A-basis allowables) and first local mode frequency (compared to 500 Hz coupling avoidance requirement). Both QoIs are directly measurable in the bench test (strain gages at the hotspot location, tap test frequency extraction) and directly computable from the FEA. The requirement-driven nature of both QoIs (LV-STD-129 strength, bus coupling avoidance) is explicitly documented. Strain rosette placement at G1 was chosen to co-locate with the model hotspot, confirming relevance.</t>
+          <t>Primary QoIs are peak von Mises stress at the critical fillet (maps directly to yield margin against LV-STD-129 and NASA-STD-5011 requirements) and first local mode frequency (maps directly to 500 Hz stiffness requirement). Secondary QoI is principal strain at rosette locations, which is measurable experimentally and directly validatable. Uncertainty propagation is performed on these same QoIs. The QoIs are explicitly tied to the flight clearance decision criteria stated in Section 1 and the modeling plan MVP-PL-342 Rev A. QoIs not relevant to current COU (fatigue, pyroshock) are explicitly excluded and noted for separate treatment.</t>
         </is>
       </c>
       <c r="G16" s="14" t="inlineStr">
@@ -2773,19 +2736,19 @@
         </is>
       </c>
       <c r="C17" s="14" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D17" s="14" t="n">
         <v>3</v>
       </c>
       <c r="E17" s="14" t="inlineStr">
         <is>
-          <t>Validation conditions cover the primary COU load cases, geometry, material, and operating environment; gaps identified and bounded</t>
+          <t>Validation test covers same geometry, same loading mode, same material, and same boundary conditions as the COU</t>
         </is>
       </c>
       <c r="F17" s="14" t="inlineStr">
         <is>
-          <t>Validation test used the production bracket from the flight lot (same geometry Rev B, same Ti-6Al-4V, same fastener class and surface finish) in a fixture replicating the deck boundary. Load magnitude (210 N ≈ 10g) covers the primary axial design case. Modal test covers the stiffness QoI. However, only a single load direction was physically tested (vertical/axial); the 8g lateral and 6g transverse cases were not experimentally validated — model predictions for those orientations rely on the validated axial-case model by analogy. Full 1.4x limit-load level was not physically applied (only 1.0x). Temperature effects assessed by a single E-perturbation run only, not validated at temperature. These gaps are acknowledged in Sections 2 and 14 but not all are experimentally bounded. Margin headroom (+1.05) partially compensates for the unvalidated load directions.</t>
+          <t>Validation bench test used a production bracket from the flight lot with Alodine surface finish, production fasteners, and a fixture replicating the deck boundary — closely matching the COU geometry and constraints. The 210 N applied load is the same as the 10g design case. Material and surface condition are identical. Modal test covers the relevant frequency regime and the specific mode shape of interest. Gaps: validation covers a single quasi-static load direction and a single bracket specimen; multi-axis simultaneous loading and lot-to-lot variation are not directly tested (covered by uncertainty propagation). Bus-level flexibility coupling is excluded from local mode validation (handled in separate IFEM). Temperature extremes and pyroshock are explicitly excluded from both the validation and COU scope. Validation conditions are judged sufficiently representative for the stated COU envelope with documented residual gaps.</t>
         </is>
       </c>
       <c r="G17" s="14" t="inlineStr">
@@ -2970,7 +2933,7 @@
       </c>
       <c r="B3" s="12" t="inlineStr">
         <is>
-          <t>All modeling plan acceptance criteria (MVP-PL-342 Rev A) are met: strain predictions at critical locations agree with bench-test measurements within 5% (criterion ±10%), first local mode prediction agrees within 3% (criterion ±5%), and mesh GCI is 5.6% (criterion &lt; 10%). Quantified uncertainty propagation via 200-sample LHS shows a 95th-percentile yield margin of +1.05 against A-basis allowables at 1.4x limit load, and first local mode 5th percentile exceeds 590 Hz against a 500 Hz requirement. Independent reviewer recreation confirmed hotspot location and magnitude within 6%. Material inputs derive from MMPDS-17 A-basis values; bolt preload is measured. Software quality is documented with CI regression testing and no open SPRs. Known limitations (thread bending, single-axis test validation, no lateral/transverse physical test, no fatigue) are explicitly scoped out of the COU and assigned to separate work packages. Model FE-RWA3-BRK-021 Rev C is accepted for flight clearance of bracket lot S/Ns RWB-052 through -058 per DOC-CLR-719, with the condition that as-built fillet radius inspections and preload measurements from the flight lot are fed into the parameter file to regenerate margins prior to final acceptance.</t>
+          <t>All modeling plan acceptance criteria defined in MVP-PL-342 Rev A are met: strain agreement within 10% (G1: −4.3%, G2: +3.4%), first local mode within 5% (−2.7%), and mesh GCI &lt;10% (5.6%). Yield margin at 1.4x limit load (95th percentile, including mesh and input variability) is +1.05 against A-basis allowable of 827 MPa; margin remains &gt;+0.9 under a hypothetical 10% allowable reduction. First local mode 5th percentile exceeds 590 Hz across all input variability, well above the 500 Hz requirement. Independent reviewer confirmed hotspot location and stress level within 6%. All inputs are traceable to aerospace-standard sources (MMPDS-17, LV-STD-129, ECSS, NASA-STD-5020) with uncertainty characterized. Model is released as FE-RWA3-BRK-021 Rev C for flight clearance of bracket S/Ns RWB-052 through -058 per DOC-CLR-719. Conditions: (1) as-built inspection results for fillet radius and preload from the flight lot must be fed into the parameter file and margins regenerated per Section 17; (2) model is not valid for fatigue, pyroshock, landing loads, or temperatures outside −30 C to +60 C; (3) any deviation in material alloy, fastener class, or fillet radius outside 1.2–1.8 mm requires reassessment.</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
